--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-with-vocabulary-property-compatible-with-import.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-with-vocabulary-property-compatible-with-import.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="52">
   <si>
     <t xml:space="preserve">VOCABULARY_TYPE</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">Type Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta Data</t>
   </si>
   <si>
     <t xml:space="preserve">ANTIBODY</t>
@@ -182,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -213,6 +216,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -260,7 +271,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -270,6 +281,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -291,7 +306,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -412,23 +427,26 @@
       <c r="J10" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K10" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -442,46 +460,46 @@
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>18</v>
@@ -495,29 +513,29 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -538,29 +556,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -590,22 +608,22 @@
         <v>5</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -660,23 +678,26 @@
       <c r="J18" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K18" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -690,46 +711,46 @@
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>18</v>
@@ -743,29 +764,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -786,29 +807,29 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -838,22 +859,22 @@
         <v>5</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>

--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-with-vocabulary-property-compatible-with-import.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-sample-type-with-vocabulary-property-compatible-with-import.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Ontology Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Type Group</t>
+    <t xml:space="preserve">Type Groups</t>
   </si>
   <si>
     <t xml:space="preserve">Meta Data</t>
@@ -306,7 +306,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
